--- a/docs/calc.xlsx
+++ b/docs/calc.xlsx
@@ -8,24 +8,36 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\from-desktop\учеба\6 СЕМ\6. Методы обработки изображений\ipm-lab-1\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F26353-203E-46FE-9E7A-4967E76085B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21EE9EC-C86E-4276-A6EE-96C16974B861}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="49">
   <si>
     <t>x</t>
   </si>
@@ -69,21 +81,6 @@
     <t>P_2</t>
   </si>
   <si>
-    <t>lp_1</t>
-  </si>
-  <si>
-    <t>lp_2</t>
-  </si>
-  <si>
-    <t>lp_3</t>
-  </si>
-  <si>
-    <t>lp_4</t>
-  </si>
-  <si>
-    <t>lp_5</t>
-  </si>
-  <si>
     <t>V</t>
   </si>
   <si>
@@ -121,13 +118,132 @@
   </si>
   <si>
     <t>цвет поверхности</t>
+  </si>
+  <si>
+    <t>P_T1</t>
+  </si>
+  <si>
+    <t>P_T2</t>
+  </si>
+  <si>
+    <t>P_T3</t>
+  </si>
+  <si>
+    <t>P_T4</t>
+  </si>
+  <si>
+    <t>P_T5</t>
+  </si>
+  <si>
+    <t>Получение глобальных координат точек</t>
+  </si>
+  <si>
+    <r>
+      <t>Получение cos(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>ϑ) с помощью вектора оси источника света O и вектора направления на точку треугольника s</t>
+    </r>
+  </si>
+  <si>
+    <t>формула 1</t>
+  </si>
+  <si>
+    <t>формула 3</t>
+  </si>
+  <si>
+    <t>Получение вектора от точки плоскости до источника света (наоборот?)</t>
+  </si>
+  <si>
+    <t>формула 5</t>
+  </si>
+  <si>
+    <t>формула 2</t>
+  </si>
+  <si>
+    <t>Получение среднего вектора h</t>
+  </si>
+  <si>
+    <t>Получение цветной освещенности E</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Получение расстояния от источника до точки треугольника R и косинуса угла </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>α</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> между направлением света s и нормалью к освещаемой поверхности N</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Получение цветной силы излучения I под углом </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>ϑ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> с помощью косинуса из предыщего пункта и заданной силы излучения в направлении оси I_0</t>
+    </r>
+  </si>
+  <si>
+    <t>Получение вектора направления наблюдения v</t>
+  </si>
+  <si>
+    <t>формула 8</t>
+  </si>
+  <si>
+    <t>Применение функции двунаправленного отражения</t>
+  </si>
+  <si>
+    <t>формула 7</t>
+  </si>
+  <si>
+    <t>формула 6</t>
+  </si>
+  <si>
+    <t>Получение яркости точки L</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -140,6 +256,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -679,14 +801,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultColWidth="15.88671875" defaultRowHeight="29.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="53.33203125" style="17" customWidth="1"/>
     <col min="2" max="16384" width="15.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C1" s="13"/>
       <c r="D1" s="3" t="s">
         <v>0</v>
@@ -698,7 +820,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
         <v>5</v>
       </c>
@@ -706,205 +828,335 @@
       <c r="C2" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="4"/>
-    </row>
-    <row r="3" spans="1:6" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D2" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="19"/>
       <c r="B3" s="6"/>
       <c r="C3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="7"/>
-    </row>
-    <row r="4" spans="1:6" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D3" s="9">
+        <v>1</v>
+      </c>
+      <c r="E3" s="9">
+        <v>1</v>
+      </c>
+      <c r="F3" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="3"/>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="4"/>
-    </row>
-    <row r="5" spans="1:6" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D4" s="2">
+        <f>(G4-D6)/$J4</f>
+        <v>-0.33333333333333331</v>
+      </c>
+      <c r="E4" s="3">
+        <f>(H4-E6)/$J4</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="4">
+        <f>(I4-F6)/$J4</f>
+        <v>-0.66666666666666663</v>
+      </c>
+      <c r="G4" s="1">
+        <f>D10</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <f>E10</f>
+        <v>2</v>
+      </c>
+      <c r="I4" s="1">
+        <f>F10</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="1">
+        <f>SQRT((D6-G4)^2+(E6-H4)^2+(F6-I4)^2)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="19"/>
       <c r="B5" s="6"/>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="7"/>
-    </row>
-    <row r="6" spans="1:6" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D5" s="5">
+        <f>(G5-D7)/$J5</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="6">
+        <f>(H5-E7)/$J5</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="7">
+        <f>(I5-F7)/$J5</f>
+        <v>-1</v>
+      </c>
+      <c r="G5" s="1">
+        <f>D10</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <f>E10</f>
+        <v>2</v>
+      </c>
+      <c r="I5" s="1">
+        <f>F10</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="1">
+        <f>SQRT((D7-G5)^2+(E7-H5)^2+(F7-I5)^2)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:6" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D6" s="9">
+        <v>1</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0</v>
+      </c>
+      <c r="F6" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="19"/>
       <c r="B7" s="6"/>
       <c r="C7" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
-    </row>
-    <row r="8" spans="1:6" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D7" s="6">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6">
+        <v>2</v>
+      </c>
+      <c r="F7" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="18" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:6" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="22"/>
       <c r="B9" s="9"/>
       <c r="C9" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="10"/>
-    </row>
-    <row r="10" spans="1:6" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D9" s="8">
+        <v>2</v>
+      </c>
+      <c r="E9" s="9">
+        <v>0</v>
+      </c>
+      <c r="F9" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="19"/>
       <c r="B10" s="6"/>
       <c r="C10" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="7"/>
-    </row>
-    <row r="11" spans="1:6" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6">
+        <v>2</v>
+      </c>
+      <c r="F10" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
+        <v>27</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1</v>
+      </c>
       <c r="F11" s="4"/>
     </row>
-    <row r="12" spans="1:6" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="21"/>
       <c r="B12" s="9"/>
       <c r="C12" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
+        <v>28</v>
+      </c>
+      <c r="D12" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0.75</v>
+      </c>
       <c r="F12" s="10"/>
     </row>
-    <row r="13" spans="1:6" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="21"/>
       <c r="B13" s="9"/>
       <c r="C13" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
+        <v>29</v>
+      </c>
+      <c r="D13" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="E13" s="9">
+        <v>0.5</v>
+      </c>
       <c r="F13" s="10"/>
     </row>
-    <row r="14" spans="1:6" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="21"/>
       <c r="B14" s="9"/>
       <c r="C14" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
+        <v>30</v>
+      </c>
+      <c r="D14" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="E14" s="9">
+        <v>0.25</v>
+      </c>
       <c r="F14" s="10"/>
     </row>
-    <row r="15" spans="1:6" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="21"/>
       <c r="B15" s="9"/>
       <c r="C15" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
+        <v>31</v>
+      </c>
+      <c r="D15" s="9">
+        <v>1</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0</v>
+      </c>
       <c r="F15" s="10"/>
     </row>
-    <row r="16" spans="1:6" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="12"/>
+        <v>14</v>
+      </c>
+      <c r="D16" s="11">
+        <v>2</v>
+      </c>
+      <c r="E16" s="11">
+        <v>2</v>
+      </c>
+      <c r="F16" s="12">
+        <v>2</v>
+      </c>
     </row>
     <row r="17" spans="1:6" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="20" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="12"/>
+        <v>15</v>
+      </c>
+      <c r="D17" s="11">
+        <v>1</v>
+      </c>
+      <c r="E17" s="11">
+        <v>0</v>
+      </c>
+      <c r="F17" s="12">
+        <v>0</v>
+      </c>
     </row>
     <row r="18" spans="1:6" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="20" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="D18" s="11"/>
+        <v>16</v>
+      </c>
+      <c r="D18" s="11">
+        <v>1</v>
+      </c>
       <c r="E18" s="11"/>
       <c r="F18" s="12"/>
     </row>
     <row r="19" spans="1:6" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="20" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="11"/>
+        <v>17</v>
+      </c>
+      <c r="D19" s="11">
+        <v>0</v>
+      </c>
       <c r="E19" s="11"/>
       <c r="F19" s="12"/>
     </row>
     <row r="20" spans="1:6" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="20" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" s="11"/>
+        <v>18</v>
+      </c>
+      <c r="D20" s="11">
+        <v>200</v>
+      </c>
       <c r="E20" s="11"/>
       <c r="F20" s="12"/>
     </row>
@@ -912,4 +1164,127 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14EA2855-9629-4837-9D49-F6C1CC803253}">
+  <dimension ref="A2:C11"/>
+  <sheetFormatPr defaultColWidth="22.88671875" defaultRowHeight="35.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="70.44140625" style="17" customWidth="1"/>
+    <col min="3" max="3" width="36" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="22.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/docs/calc.xlsx
+++ b/docs/calc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\from-desktop\учеба\6 СЕМ\6. Методы обработки изображений\ipm-lab-1\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21EE9EC-C86E-4276-A6EE-96C16974B861}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6DAE1BD-15F7-4460-A460-C916149CD3F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -829,10 +829,10 @@
         <v>3</v>
       </c>
       <c r="D2" s="3">
-        <v>0.5</v>
+        <v>500</v>
       </c>
       <c r="E2" s="3">
-        <v>0.5</v>
+        <v>500</v>
       </c>
       <c r="F2" s="4">
         <v>0</v>
@@ -845,13 +845,13 @@
         <v>4</v>
       </c>
       <c r="D3" s="9">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="E3" s="9">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="F3" s="10">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1127,7 +1127,7 @@
         <v>16</v>
       </c>
       <c r="D18" s="11">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E18" s="11"/>
       <c r="F18" s="12"/>
@@ -1141,7 +1141,7 @@
         <v>17</v>
       </c>
       <c r="D19" s="11">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E19" s="11"/>
       <c r="F19" s="12"/>
@@ -1223,7 +1223,7 @@
     </row>
     <row r="6" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" s="17" t="s">
         <v>41</v>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="7" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" s="17" t="s">
         <v>40</v>
@@ -1245,7 +1245,7 @@
     </row>
     <row r="8" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" s="17" t="s">
         <v>43</v>
@@ -1253,7 +1253,7 @@
     </row>
     <row r="9" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>39</v>
@@ -1264,7 +1264,7 @@
     </row>
     <row r="10" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>45</v>
@@ -1275,7 +1275,7 @@
     </row>
     <row r="11" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" s="17" t="s">
         <v>48</v>

--- a/docs/calc.xlsx
+++ b/docs/calc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\from-desktop\учеба\6 СЕМ\6. Методы обработки изображений\ipm-lab-1\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6DAE1BD-15F7-4460-A460-C916149CD3F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5659EB-AFB3-48C6-B6D6-8BD70202584F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
   <si>
     <t>x</t>
   </si>
@@ -237,6 +237,15 @@
   </si>
   <si>
     <t>Получение яркости точки L</t>
+  </si>
+  <si>
+    <t>№</t>
+  </si>
+  <si>
+    <t>Действие</t>
+  </si>
+  <si>
+    <t>Формула</t>
   </si>
 </sst>
 </file>
@@ -1168,7 +1177,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14EA2855-9629-4837-9D49-F6C1CC803253}">
-  <dimension ref="A2:C11"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultColWidth="22.88671875" defaultRowHeight="35.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" style="1" customWidth="1"/>
@@ -1177,6 +1186,17 @@
     <col min="4" max="16384" width="22.88671875" style="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
     <row r="2" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>

--- a/docs/calc.xlsx
+++ b/docs/calc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\from-desktop\учеба\6 СЕМ\6. Методы обработки изображений\ipm-lab-1\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5659EB-AFB3-48C6-B6D6-8BD70202584F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B9375B3-F8D1-4EB9-BBDC-D8392CE82282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -39,15 +39,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
   <si>
-    <t>x</t>
-  </si>
-  <si>
-    <t>y</t>
-  </si>
-  <si>
-    <t>z</t>
-  </si>
-  <si>
     <t>I_01</t>
   </si>
   <si>
@@ -246,6 +237,15 @@
   </si>
   <si>
     <t>Формула</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x (R) </t>
+  </si>
+  <si>
+    <t>y (G)</t>
+  </si>
+  <si>
+    <t>z (B)</t>
   </si>
 </sst>
 </file>
@@ -462,7 +462,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -470,34 +470,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
@@ -515,20 +488,71 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -810,366 +834,359 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultColWidth="15.88671875" defaultRowHeight="29.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="53.33203125" style="17" customWidth="1"/>
-    <col min="2" max="16384" width="15.88671875" style="1"/>
+    <col min="1" max="1" width="53.33203125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="15.88671875" style="1"/>
+    <col min="3" max="5" width="15.88671875" style="21"/>
+    <col min="6" max="16384" width="15.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C1" s="13"/>
-      <c r="D1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="3" t="s">
+    <row r="1" spans="1:9" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="4"/>
+      <c r="C1" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="10">
+        <v>500</v>
+      </c>
+      <c r="D2" s="10">
+        <v>500</v>
+      </c>
+      <c r="E2" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="23"/>
+      <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
+      <c r="C3" s="12">
+        <v>1000</v>
+      </c>
+      <c r="D3" s="12">
+        <v>1000</v>
+      </c>
+      <c r="E3" s="13">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="13" t="s">
+      <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3">
-        <v>500</v>
-      </c>
-      <c r="E2" s="3">
-        <v>500</v>
-      </c>
-      <c r="F2" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="19"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="9">
-        <v>1000</v>
-      </c>
-      <c r="E3" s="9">
-        <v>1000</v>
-      </c>
-      <c r="F3" s="10">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="2">
-        <f>(G4-D6)/$J4</f>
+      <c r="C4" s="14">
+        <f>(F4-C6)/$I4</f>
         <v>-0.33333333333333331</v>
       </c>
-      <c r="E4" s="3">
-        <f>(H4-E6)/$J4</f>
+      <c r="D4" s="10">
+        <f>(G4-D6)/$I4</f>
         <v>0.66666666666666663</v>
       </c>
-      <c r="F4" s="4">
-        <f>(I4-F6)/$J4</f>
+      <c r="E4" s="11">
+        <f>(H4-E6)/$I4</f>
         <v>-0.66666666666666663</v>
+      </c>
+      <c r="F4" s="1">
+        <f>C10</f>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
         <f>D10</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" s="1">
         <f>E10</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" s="1">
-        <f>F10</f>
-        <v>0</v>
-      </c>
-      <c r="J4" s="1">
-        <f>SQRT((D6-G4)^2+(E6-H4)^2+(F6-I4)^2)</f>
+        <f>SQRT((C6-F4)^2+(D6-G4)^2+(E6-H4)^2)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="19"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="5">
-        <f>(G5-D7)/$J5</f>
-        <v>0</v>
-      </c>
-      <c r="E5" s="6">
-        <f>(H5-E7)/$J5</f>
-        <v>0</v>
-      </c>
-      <c r="F5" s="7">
-        <f>(I5-F7)/$J5</f>
+    <row r="5" spans="1:9" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="23"/>
+      <c r="B5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="15">
+        <f>(F5-C7)/$I5</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="16">
+        <f>(G5-D7)/$I5</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="17">
+        <f>(H5-E7)/$I5</f>
         <v>-1</v>
+      </c>
+      <c r="F5" s="1">
+        <f>C10</f>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
         <f>D10</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" s="1">
         <f>E10</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="1">
+        <f>SQRT((C7-F5)^2+(D7-G5)^2+(E7-H5)^2)</f>
         <v>2</v>
       </c>
-      <c r="I5" s="1">
-        <f>F10</f>
-        <v>0</v>
-      </c>
-      <c r="J5" s="1">
-        <f>SQRT((D7-G5)^2+(E7-H5)^2+(F7-I5)^2)</f>
+    </row>
+    <row r="6" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="12">
+        <v>1</v>
+      </c>
+      <c r="D6" s="12">
+        <v>0</v>
+      </c>
+      <c r="E6" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
+    <row r="7" spans="1:9" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="23"/>
+      <c r="B7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="16">
+        <v>0</v>
+      </c>
+      <c r="D7" s="16">
+        <v>2</v>
+      </c>
+      <c r="E7" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="14">
+        <v>0</v>
+      </c>
+      <c r="D8" s="10">
+        <v>0</v>
+      </c>
+      <c r="E8" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="25"/>
+      <c r="B9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="18">
+        <v>2</v>
+      </c>
+      <c r="D9" s="12">
+        <v>0</v>
+      </c>
+      <c r="E9" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="26"/>
+      <c r="B10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="15">
+        <v>0</v>
+      </c>
+      <c r="D10" s="16">
+        <v>2</v>
+      </c>
+      <c r="E10" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="9">
+      <c r="C11" s="10">
+        <v>0</v>
+      </c>
+      <c r="D11" s="10">
         <v>1</v>
       </c>
-      <c r="E6" s="9">
-        <v>0</v>
-      </c>
-      <c r="F6" s="10">
+      <c r="E11" s="11"/>
+    </row>
+    <row r="12" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27"/>
+      <c r="B12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="D12" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="E12" s="13"/>
+    </row>
+    <row r="13" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="27"/>
+      <c r="B13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="D13" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="E13" s="13"/>
+    </row>
+    <row r="14" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="27"/>
+      <c r="B14" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="D14" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="E14" s="13"/>
+    </row>
+    <row r="15" spans="1:9" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="23"/>
+      <c r="B15" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="12">
+        <v>1</v>
+      </c>
+      <c r="D15" s="12">
+        <v>0</v>
+      </c>
+      <c r="E15" s="13"/>
+    </row>
+    <row r="16" spans="1:9" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="19">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="19"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="6">
-        <v>0</v>
-      </c>
-      <c r="E7" s="6">
+      <c r="D16" s="19">
         <v>2</v>
       </c>
-      <c r="F7" s="7">
+      <c r="E16" s="20">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="18" t="s">
+    <row r="17" spans="1:5" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="22"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="16" t="s">
+      <c r="B17" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="8">
-        <v>2</v>
-      </c>
-      <c r="E9" s="9">
-        <v>0</v>
-      </c>
-      <c r="F9" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="19"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="14" t="s">
+      <c r="C17" s="19">
+        <v>1</v>
+      </c>
+      <c r="D17" s="19">
+        <v>0</v>
+      </c>
+      <c r="E17" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="5">
-        <v>0</v>
-      </c>
-      <c r="E10" s="6">
-        <v>2</v>
-      </c>
-      <c r="F10" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="18" t="s">
+      <c r="C18" s="29">
+        <v>0.5</v>
+      </c>
+      <c r="D18" s="28"/>
+      <c r="E18" s="30"/>
+    </row>
+    <row r="19" spans="1:5" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="29">
+        <v>0.5</v>
+      </c>
+      <c r="D19" s="28"/>
+      <c r="E19" s="30"/>
+    </row>
+    <row r="20" spans="1:5" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="3">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3">
-        <v>1</v>
-      </c>
-      <c r="F11" s="4"/>
-    </row>
-    <row r="12" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="21"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="E12" s="9">
-        <v>0.75</v>
-      </c>
-      <c r="F12" s="10"/>
-    </row>
-    <row r="13" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="21"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="E13" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="F13" s="10"/>
-    </row>
-    <row r="14" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="21"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="9">
-        <v>0.75</v>
-      </c>
-      <c r="E14" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="F14" s="10"/>
-    </row>
-    <row r="15" spans="1:10" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="21"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" s="9">
-        <v>1</v>
-      </c>
-      <c r="E15" s="9">
-        <v>0</v>
-      </c>
-      <c r="F15" s="10"/>
-    </row>
-    <row r="16" spans="1:10" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="11">
-        <v>2</v>
-      </c>
-      <c r="E16" s="11">
-        <v>2</v>
-      </c>
-      <c r="F16" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="15" t="s">
+      <c r="B20" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="11">
-        <v>1</v>
-      </c>
-      <c r="E17" s="11">
-        <v>0</v>
-      </c>
-      <c r="F17" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="E18" s="11"/>
-      <c r="F18" s="12"/>
-    </row>
-    <row r="19" spans="1:6" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="E19" s="11"/>
-      <c r="F19" s="12"/>
-    </row>
-    <row r="20" spans="1:6" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" s="11">
+      <c r="C20" s="29">
         <v>200</v>
       </c>
-      <c r="E20" s="11"/>
-      <c r="F20" s="12"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="30"/>
     </row>
   </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A11:A15"/>
+    <mergeCell ref="C18:E18"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1181,127 +1198,127 @@
   <sheetFormatPr defaultColWidth="22.88671875" defaultRowHeight="35.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="70.44140625" style="17" customWidth="1"/>
+    <col min="2" max="2" width="70.44140625" style="8" customWidth="1"/>
     <col min="3" max="3" width="36" style="1" customWidth="1"/>
     <col min="4" max="16384" width="22.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>50</v>
+        <v>46</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="17" t="s">
-        <v>36</v>
+      <c r="B3" s="8" t="s">
+        <v>33</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="17" t="s">
-        <v>33</v>
+      <c r="B4" s="8" t="s">
+        <v>30</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="17" t="s">
-        <v>42</v>
+      <c r="B5" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>6</v>
       </c>
-      <c r="B6" s="17" t="s">
-        <v>41</v>
+      <c r="B6" s="8" t="s">
+        <v>38</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>7</v>
       </c>
-      <c r="B7" s="17" t="s">
-        <v>40</v>
+      <c r="B7" s="8" t="s">
+        <v>37</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>8</v>
       </c>
-      <c r="B8" s="17" t="s">
-        <v>43</v>
+      <c r="B8" s="8" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>9</v>
       </c>
-      <c r="B9" s="17" t="s">
-        <v>39</v>
+      <c r="B9" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>10</v>
       </c>
-      <c r="B10" s="17" t="s">
-        <v>45</v>
+      <c r="B10" s="8" t="s">
+        <v>42</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>11</v>
       </c>
-      <c r="B11" s="17" t="s">
-        <v>48</v>
+      <c r="B11" s="8" t="s">
+        <v>45</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/docs/calc.xlsx
+++ b/docs/calc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\from-desktop\учеба\6 СЕМ\6. Методы обработки изображений\ipm-lab-1\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B9375B3-F8D1-4EB9-BBDC-D8392CE82282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7BD4431-137B-4C36-8752-A2A2C7999084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="53">
   <si>
     <t>I_01</t>
   </si>
@@ -246,6 +246,9 @@
   </si>
   <si>
     <t>z (B)</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -462,7 +465,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -552,6 +555,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -896,15 +908,15 @@
       </c>
       <c r="C4" s="14">
         <f>(F4-C6)/$I4</f>
-        <v>-0.33333333333333331</v>
+        <v>-0.2672612419124244</v>
       </c>
       <c r="D4" s="10">
         <f>(G4-D6)/$I4</f>
-        <v>0.66666666666666663</v>
+        <v>0.53452248382484879</v>
       </c>
       <c r="E4" s="11">
         <f>(H4-E6)/$I4</f>
-        <v>-0.66666666666666663</v>
+        <v>0.80178372573727319</v>
       </c>
       <c r="F4" s="1">
         <f>C10</f>
@@ -916,11 +928,11 @@
       </c>
       <c r="H4" s="1">
         <f>E10</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I4" s="1">
         <f>SQRT((C6-F4)^2+(D6-G4)^2+(E6-H4)^2)</f>
-        <v>3</v>
+        <v>3.7416573867739413</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -938,7 +950,7 @@
       </c>
       <c r="E5" s="17">
         <f>(H5-E7)/$I5</f>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F5" s="1">
         <f>C10</f>
@@ -950,11 +962,11 @@
       </c>
       <c r="H5" s="1">
         <f>E10</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I5" s="1">
         <f>SQRT((C7-F5)^2+(D7-G5)^2+(E7-H5)^2)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1026,14 +1038,14 @@
       <c r="B10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="15">
-        <v>0</v>
-      </c>
-      <c r="D10" s="16">
+      <c r="C10" s="18">
+        <v>0</v>
+      </c>
+      <c r="D10" s="12">
         <v>2</v>
       </c>
-      <c r="E10" s="17">
-        <v>0</v>
+      <c r="E10" s="13">
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1043,65 +1055,75 @@
       <c r="B11" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="10">
-        <v>0</v>
+      <c r="C11" s="14">
+        <v>-100</v>
       </c>
       <c r="D11" s="10">
-        <v>1</v>
-      </c>
-      <c r="E11" s="11"/>
+        <v>-100</v>
+      </c>
+      <c r="E11" s="31" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="12" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="27"/>
       <c r="B12" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="12">
-        <v>0.25</v>
+      <c r="C12" s="18">
+        <v>0</v>
       </c>
       <c r="D12" s="12">
-        <v>0.75</v>
-      </c>
-      <c r="E12" s="13"/>
+        <v>0</v>
+      </c>
+      <c r="E12" s="32" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="13" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="27"/>
       <c r="B13" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="12">
-        <v>0.5</v>
+      <c r="C13" s="18">
+        <v>0</v>
       </c>
       <c r="D13" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="E13" s="13"/>
+        <v>15</v>
+      </c>
+      <c r="E13" s="32" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="14" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="27"/>
       <c r="B14" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="12">
-        <v>0.75</v>
+      <c r="C14" s="18">
+        <v>0</v>
       </c>
       <c r="D14" s="12">
-        <v>0.25</v>
-      </c>
-      <c r="E14" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="E14" s="32" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="15" spans="1:9" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="23"/>
       <c r="B15" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="12">
-        <v>1</v>
-      </c>
-      <c r="D15" s="12">
-        <v>0</v>
-      </c>
-      <c r="E15" s="13"/>
+      <c r="C15" s="15">
+        <v>100</v>
+      </c>
+      <c r="D15" s="16">
+        <v>100</v>
+      </c>
+      <c r="E15" s="33" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="16" spans="1:9" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
@@ -1110,13 +1132,13 @@
       <c r="B16" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="19">
+      <c r="C16" s="16">
         <v>2</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="16">
         <v>2</v>
       </c>
-      <c r="E16" s="20">
+      <c r="E16" s="17">
         <v>2</v>
       </c>
     </row>

--- a/docs/calc.xlsx
+++ b/docs/calc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\from-desktop\учеба\6 СЕМ\6. Методы обработки изображений\ipm-lab-1\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7BD4431-137B-4C36-8752-A2A2C7999084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5B02C61-68BD-4C0E-B0DF-83513B72DE5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="48">
   <si>
     <t>I_01</t>
   </si>
@@ -109,21 +109,6 @@
   </si>
   <si>
     <t>цвет поверхности</t>
-  </si>
-  <si>
-    <t>P_T1</t>
-  </si>
-  <si>
-    <t>P_T2</t>
-  </si>
-  <si>
-    <t>P_T3</t>
-  </si>
-  <si>
-    <t>P_T4</t>
-  </si>
-  <si>
-    <t>P_T5</t>
   </si>
   <si>
     <t>Получение глобальных координат точек</t>
@@ -858,13 +843,13 @@
     <row r="1" spans="1:9" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="4"/>
       <c r="C1" s="10" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -875,10 +860,10 @@
         <v>0</v>
       </c>
       <c r="C2" s="10">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="D2" s="10">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="E2" s="11">
         <v>0</v>
@@ -908,15 +893,15 @@
       </c>
       <c r="C4" s="14">
         <f>(F4-C6)/$I4</f>
-        <v>-0.2672612419124244</v>
+        <v>-0.54882129994845175</v>
       </c>
       <c r="D4" s="10">
         <f>(G4-D6)/$I4</f>
-        <v>0.53452248382484879</v>
+        <v>0.76834981992783236</v>
       </c>
       <c r="E4" s="11">
         <f>(H4-E6)/$I4</f>
-        <v>0.80178372573727319</v>
+        <v>0.32929277996907103</v>
       </c>
       <c r="F4" s="1">
         <f>C10</f>
@@ -932,7 +917,7 @@
       </c>
       <c r="I4" s="1">
         <f>SQRT((C6-F4)^2+(D6-G4)^2+(E6-H4)^2)</f>
-        <v>3.7416573867739413</v>
+        <v>9.1104335791442992</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -950,7 +935,7 @@
       </c>
       <c r="E5" s="17">
         <f>(H5-E7)/$I5</f>
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F5" s="1">
         <f>C10</f>
@@ -966,7 +951,7 @@
       </c>
       <c r="I5" s="1">
         <f>SQRT((C7-F5)^2+(D7-G5)^2+(E7-H5)^2)</f>
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -977,10 +962,10 @@
         <v>6</v>
       </c>
       <c r="C6" s="12">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D6" s="12">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E6" s="13">
         <v>2</v>
@@ -998,7 +983,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="17">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1052,9 +1037,7 @@
       <c r="A11" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>24</v>
-      </c>
+      <c r="B11" s="7"/>
       <c r="C11" s="14">
         <v>-100</v>
       </c>
@@ -1062,14 +1045,12 @@
         <v>-100</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="27"/>
-      <c r="B12" s="7" t="s">
-        <v>25</v>
-      </c>
+      <c r="B12" s="7"/>
       <c r="C12" s="18">
         <v>0</v>
       </c>
@@ -1077,52 +1058,46 @@
         <v>0</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="27"/>
-      <c r="B13" s="7" t="s">
-        <v>26</v>
-      </c>
+      <c r="B13" s="7"/>
       <c r="C13" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13" s="12">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="27"/>
-      <c r="B14" s="7" t="s">
-        <v>27</v>
-      </c>
+      <c r="B14" s="7"/>
       <c r="C14" s="18">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D14" s="12">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="23"/>
-      <c r="B15" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="B15" s="7"/>
       <c r="C15" s="15">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D15" s="16">
         <v>100</v>
       </c>
       <c r="E15" s="33" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1227,13 +1202,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1241,10 +1216,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1252,10 +1227,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1263,10 +1238,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1274,10 +1249,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1285,10 +1260,10 @@
         <v>6</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1296,10 +1271,10 @@
         <v>7</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1307,7 +1282,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1315,10 +1290,10 @@
         <v>9</v>
       </c>
       <c r="B9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1326,10 +1301,10 @@
         <v>10</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1337,10 +1312,10 @@
         <v>11</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
